--- a/Documentacion Sprint (01 - 11)/Sprint 7 documentacion/Sprint_07_Backlog_ICARO.xlsx
+++ b/Documentacion Sprint (01 - 11)/Sprint 7 documentacion/Sprint_07_Backlog_ICARO.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 7 documentacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentacion Sprint (01 - 11)\Sprint 7 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28FF001-7CBD-4D06-BE7C-58CBB2C380E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DD5207-3D93-4226-A0E5-205A9B967172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5415" yWindow="1125" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SPRINT BACKLOG" sheetId="4" r:id="rId1"/>
     <sheet name="RESUMEN DE VELOCIDAD" sheetId="3" r:id="rId2"/>
-    <sheet name="Glosario" sheetId="5" r:id="rId3"/>
-    <sheet name="Resumen Casos de Prueba" sheetId="2" r:id="rId4"/>
+    <sheet name="Resumen Casos de Prueba" sheetId="2" r:id="rId3"/>
+    <sheet name="Glosario" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="302">
   <si>
     <t>ID</t>
   </si>
@@ -858,9 +858,6 @@
     <t>backend/src/routes/ordenesCambio.routes.js, backend/src/routes/compras.routes.js, backend/tests/sprint7_gerencial_ordenes.test.js – CP-165 a CP-168</t>
   </si>
   <si>
-    <t>RESUMEN DE VELOCIDAD — Sprint 06</t>
-  </si>
-  <si>
     <t>Métrica</t>
   </si>
   <si>
@@ -1078,13 +1075,19 @@
   </si>
   <si>
     <t>TOTALES</t>
+  </si>
+  <si>
+    <t>Los estados presentados en este documento corresponden al estado del Product/Sprint Backlog al cierre del Sprint respectivo. Debido a la naturaleza iterativa e incremental del proyecto, los elementos identificados como pendientes, diferidos o parcialmente implementados pudieron ser desarrollados y completados en sprints posteriores. Para conocer el estado definitivo de cada historia de usuario o historia técnica, debe consultarse el Product Backlog Consolidado al cierre del proyecto.</t>
+  </si>
+  <si>
+    <t>RESUMEN DE VELOCIDAD — Sprint 07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1197,8 +1200,15 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1247,8 +1257,13 @@
         <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1371,11 +1386,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1447,6 +1478,9 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1522,8 +1556,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Notas" xfId="1" builtinId="10"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
@@ -1935,7 +1970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84881648-78FC-44F0-9E17-BFFD3CFC7077}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -1950,124 +1985,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
     </row>
     <row r="3" spans="1:12" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:12" ht="24">
       <c r="A4" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="35">
         <v>46167</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="31"/>
       <c r="G4" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="34">
+      <c r="H4" s="35">
         <v>46171</v>
       </c>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="31"/>
     </row>
     <row r="5" spans="1:12" ht="128.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="40"/>
       <c r="G5" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="31"/>
     </row>
     <row r="6" spans="1:12" ht="24">
       <c r="A6" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="43"/>
       <c r="G6" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="H6" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="46"/>
     </row>
     <row r="7" spans="1:12" ht="30">
       <c r="A7" s="4" t="s">
@@ -2336,13 +2371,13 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="35" t="s">
-        <v>300</v>
-      </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
+      <c r="A14" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
       <c r="F14" s="17">
         <v>48</v>
       </c>
@@ -2355,19 +2390,85 @@
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
     </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H6:L6"/>
+  <mergeCells count="12">
+    <mergeCell ref="A16:G22"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2385,30 +2486,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="46" t="s">
-        <v>227</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="A1" s="47" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>230</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B3" s="9">
         <v>48</v>
@@ -2417,12 +2518,12 @@
         <v>48</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B4" s="9">
         <v>5</v>
@@ -2431,12 +2532,12 @@
         <v>5</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B5" s="9">
         <v>1</v>
@@ -2450,7 +2551,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B6" s="9">
         <v>6</v>
@@ -2459,12 +2560,12 @@
         <v>6</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B7" s="9">
         <v>6</v>
@@ -2478,7 +2579,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B8" s="9">
         <v>0</v>
@@ -2487,12 +2588,12 @@
         <v>0</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B9" s="9">
         <v>0</v>
@@ -2501,12 +2602,12 @@
         <v>0</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B10" s="9">
         <v>48</v>
@@ -2515,12 +2616,12 @@
         <v>48</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B11" s="10">
         <v>1</v>
@@ -2529,12 +2630,12 @@
         <v>1</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B12" s="9">
         <v>46</v>
@@ -2543,12 +2644,12 @@
         <v>46</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B13" s="10">
         <v>1</v>
@@ -2557,12 +2658,12 @@
         <v>1</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B14" s="9">
         <v>168</v>
@@ -2571,7 +2672,7 @@
         <v>168</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -2586,206 +2687,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF91D80-AAAC-43AB-A668-69EC165CF06C}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="32.85546875" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="48" t="s">
-        <v>254</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="14" t="s">
-        <v>294</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>295</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>299</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -2798,14 +2699,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="19" t="s">
@@ -3753,4 +3654,204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF91D80-AAAC-43AB-A668-69EC165CF06C}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>298</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>